--- a/recipes/onion-garlic-free-indian/focus-states/10-uttar-pradesh/excel/uttar-pradesh-recipes.xlsx
+++ b/recipes/onion-garlic-free-indian/focus-states/10-uttar-pradesh/excel/uttar-pradesh-recipes.xlsx
@@ -104,7 +104,7 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="009A3412"/>
-      <sz val="16"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="19">
@@ -259,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -358,6 +358,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="18" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1465,7 +1468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1477,7 +1480,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Bhindi ki Sabzi</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Bhindi ki Sabzi</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1487,7 +1490,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Uttar Pradesh kitchen  ·  Side  ·  Awadhi, Braj and Purvanchal sattvic</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Uttar Pradesh  ·  Side</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -1507,44 +1510,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Prep 10 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -1746,37 +1749,203 @@
       <c r="C22" s="46" t="n"/>
       <c r="D22" s="46" t="n"/>
     </row>
-    <row r="23" ht="36" customHeight="1">
+    <row r="23" ht="66" customHeight="1">
       <c r="A23" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="48" t="inlineStr">
         <is>
-          <t>Fry uncovered until no slime.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C23" s="49" t="n"/>
       <c r="D23" s="49" t="n"/>
     </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel kadhai or saucepan — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Fry uncovered until no slime. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="22" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>kcal 40  ·  Protein 2 g  ·  Carbs 8 g  ·  Fat 0 g  ·  Fibre 3 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="72" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>For Bhindi ki Sabzi: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B37" s="52" t="n"/>
+      <c r="C37" s="52" t="n"/>
+      <c r="D37" s="52" t="n"/>
+    </row>
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Serve family-style in a steel bowl. Keep a lid on at the pass so it does not skin. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B38" s="50" t="n"/>
+      <c r="C38" s="50" t="n"/>
+      <c r="D38" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="31">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -1790,7 +1959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1802,7 +1971,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Lauki Sabzi</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Lauki Sabzi</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1812,7 +1981,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Uttar Pradesh kitchen  ·  Side  ·  Awadhi, Braj and Purvanchal sattvic</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Uttar Pradesh  ·  Side</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -1832,44 +2001,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Prep 10 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -2053,36 +2222,202 @@
       <c r="C21" s="46" t="n"/>
       <c r="D21" s="46" t="n"/>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="66" customHeight="1">
       <c r="A22" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B22" s="48" t="inlineStr">
         <is>
-          <t>Simmer until soft.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C22" s="49" t="n"/>
       <c r="D22" s="49" t="n"/>
     </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel kadhai or saucepan — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Simmer until soft. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="n"/>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="22" t="n"/>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>kcal 131  ·  Protein 5 g  ·  Carbs 20 g  ·  Fat 4 g  ·  Fibre 4 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B31" s="50" t="n"/>
+      <c r="C31" s="50" t="n"/>
+      <c r="D31" s="50" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="48" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="72" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>For Lauki Sabzi: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="26" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B36" s="52" t="n"/>
+      <c r="C36" s="52" t="n"/>
+      <c r="D36" s="52" t="n"/>
+    </row>
+    <row r="37" ht="64" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Serve family-style in a steel bowl. Keep a lid on at the pass so it does not skin. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B37" s="50" t="n"/>
+      <c r="C37" s="50" t="n"/>
+      <c r="D37" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="30">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2096,7 +2431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2108,7 +2443,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Jeera Aloo</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Jeera Aloo</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2118,7 +2453,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Uttar Pradesh kitchen  ·  Side  ·  Awadhi, Braj and Purvanchal sattvic</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Uttar Pradesh  ·  Side</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2138,44 +2473,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Prep 10 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -2377,37 +2712,203 @@
       <c r="C22" s="46" t="n"/>
       <c r="D22" s="46" t="n"/>
     </row>
-    <row r="23" ht="36" customHeight="1">
+    <row r="23" ht="66" customHeight="1">
       <c r="A23" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="48" t="inlineStr">
         <is>
-          <t>Fry until golden.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C23" s="49" t="n"/>
       <c r="D23" s="49" t="n"/>
     </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. If using potato, cook until tender, drain, and steam-dry so the mix is not wet.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel kadhai or saucepan — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Fry until golden. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="22" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>kcal 81  ·  Protein 2 g  ·  Carbs 18 g  ·  Fat 0 g  ·  Fibre 2 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="72" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>For Jeera Aloo: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B37" s="52" t="n"/>
+      <c r="C37" s="52" t="n"/>
+      <c r="D37" s="52" t="n"/>
+    </row>
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Serve family-style in a steel bowl. Keep a lid on at the pass so it does not skin. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B38" s="50" t="n"/>
+      <c r="C38" s="50" t="n"/>
+      <c r="D38" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="31">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2421,7 +2922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2433,7 +2934,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Bedmi Puri</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Bedmi Puri</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2443,7 +2944,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Uttar Pradesh kitchen  ·  Bread  ·  Awadhi, Braj and Purvanchal sattvic</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Uttar Pradesh  ·  Bread</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2463,44 +2964,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>Prep 25 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -2684,36 +3185,202 @@
       <c r="C21" s="46" t="n"/>
       <c r="D21" s="46" t="n"/>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="66" customHeight="1">
       <c r="A22" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B22" s="48" t="inlineStr">
         <is>
-          <t>Roll thick, fry until brown and puffed.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel kadhai for frying — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C22" s="49" t="n"/>
       <c r="D22" s="49" t="n"/>
     </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Steel kadhai for frying — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Roll thick, fry until brown and puffed. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: bread is cooked through, no wet dough in the centre, light brown spots on the face.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Hold wrapped in a clean cloth in a covered steel box up to 30 minutes. Refresh on a hot tawa 20 seconds if needed. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="n"/>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="22" t="n"/>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>kcal 451  ·  Protein 19 g  ·  Carbs 78 g  ·  Fat 9 g  ·  Fibre 15 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B31" s="50" t="n"/>
+      <c r="C31" s="50" t="n"/>
+      <c r="D31" s="50" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="48" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="72" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>For Bedmi Puri: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="26" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B36" s="52" t="n"/>
+      <c r="C36" s="52" t="n"/>
+      <c r="D36" s="52" t="n"/>
+    </row>
+    <row r="37" ht="64" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Send to table wrapped. Do not stack in plastic or they sweat. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B37" s="50" t="n"/>
+      <c r="C37" s="50" t="n"/>
+      <c r="D37" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="30">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2727,7 +3394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2739,7 +3406,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Phulka</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Phulka</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2749,7 +3416,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Uttar Pradesh kitchen  ·  Bread  ·  Awadhi, Braj and Purvanchal sattvic</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Uttar Pradesh  ·  Bread</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2769,44 +3436,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Prep 15 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -2936,33 +3603,186 @@
       <c r="C18" s="46" t="n"/>
       <c r="D18" s="46" t="n"/>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="54" customHeight="1">
       <c r="A19" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>Puff on iron tawa / flame.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Cast-iron tawa (not aluminium). Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C19" s="49" t="n"/>
       <c r="D19" s="49" t="n"/>
     </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Puff on iron tawa / flame. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: bread is cooked through, no wet dough in the centre, light brown spots on the face.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Hold wrapped in a clean cloth in a covered steel box up to 30 minutes. Refresh on a hot tawa 20 seconds if needed. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="n"/>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="22" t="n"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>kcal 318  ·  Protein 9 g  ·  Carbs 54 g  ·  Fat 8 g  ·  Fibre 8 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B27" s="50" t="n"/>
+      <c r="C27" s="50" t="n"/>
+      <c r="D27" s="50" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="72" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>For Phulka: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B32" s="52" t="n"/>
+      <c r="C32" s="52" t="n"/>
+      <c r="D32" s="52" t="n"/>
+    </row>
+    <row r="33" ht="64" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Send to table wrapped. Do not stack in plastic or they sweat. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="26">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2976,7 +3796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2988,7 +3808,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Poori</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Poori</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2998,7 +3818,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Uttar Pradesh kitchen  ·  Bread  ·  Awadhi, Braj and Purvanchal sattvic</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Uttar Pradesh  ·  Bread</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3018,44 +3838,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Prep 15 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -3203,34 +4023,187 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="66" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Fry in steel.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel kadhai for frying — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="49" t="n"/>
     </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Fry in steel. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: bread is cooked through, no wet dough in the centre, light brown spots on the face.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Hold wrapped in a clean cloth in a covered steel box up to 30 minutes. Refresh on a hot tawa 20 seconds if needed. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>kcal 380  ·  Protein 9 g  ·  Carbs 54 g  ·  Fat 15 g  ·  Fibre 8 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="n"/>
+      <c r="C28" s="50" t="n"/>
+      <c r="D28" s="50" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>For Poori: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Send to table wrapped. Do not stack in plastic or they sweat. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="27">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3244,7 +4217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3256,7 +4229,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Agra Petha</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Agra Petha</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3266,7 +4239,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Uttar Pradesh kitchen  ·  Sweet  ·  Awadhi, Braj and Purvanchal sattvic</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Uttar Pradesh  ·  Sweet</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3286,44 +4259,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>60 min</t>
+          <t>Prep 20 min · Cook 40 min</t>
         </is>
       </c>
     </row>
@@ -3471,34 +4444,187 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="66" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Boil cubes, candy in steel syrup.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="49" t="n"/>
     </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Boil cubes, candy in steel syrup. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>kcal 332  ·  Protein 3 g  ·  Carbs 76 g  ·  Fat 3 g  ·  Fibre 2 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="n"/>
+      <c r="C28" s="50" t="n"/>
+      <c r="D28" s="50" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>For Agra Petha: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Cut even portions. Garnish with nuts only if the allergen card allows. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="27">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3512,7 +4638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3524,7 +4650,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Mathura Pedha</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Mathura Pedha</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3534,7 +4660,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Uttar Pradesh kitchen  ·  Sweet  ·  Awadhi, Braj and Purvanchal sattvic</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Uttar Pradesh  ·  Sweet</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3554,44 +4680,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Prep 15 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -3721,33 +4847,186 @@
       <c r="C18" s="46" t="n"/>
       <c r="D18" s="46" t="n"/>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="66" customHeight="1">
       <c r="A19" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>Cook in steel, shape pedas.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C19" s="49" t="n"/>
       <c r="D19" s="49" t="n"/>
     </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Cook in steel, shape pedas. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="n"/>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="22" t="n"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>kcal 308  ·  Protein 7 g  ·  Carbs 38 g  ·  Fat 13 g  ·  Fibre 0 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B27" s="50" t="n"/>
+      <c r="C27" s="50" t="n"/>
+      <c r="D27" s="50" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="72" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>For Mathura Pedha: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B32" s="52" t="n"/>
+      <c r="C32" s="52" t="n"/>
+      <c r="D32" s="52" t="n"/>
+    </row>
+    <row r="33" ht="64" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Cut even portions. Garnish with nuts only if the allergen card allows. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="26">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3761,7 +5040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3773,7 +5052,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Balushahi</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Balushahi</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3783,7 +5062,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Uttar Pradesh kitchen  ·  Sweet  ·  Awadhi, Braj and Purvanchal sattvic</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Uttar Pradesh  ·  Sweet</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3803,44 +5082,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>50 min</t>
+          <t>Prep 25 min · Cook 25 min</t>
         </is>
       </c>
     </row>
@@ -4006,35 +5285,188 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="66" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Fry on low, soak in syrup made in steel.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel kadhai for frying — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Fry on low, soak in syrup made in steel. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>kcal 563  ·  Protein 8 g  ·  Carbs 113 g  ·  Fat 9 g  ·  Fibre 2 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B29" s="50" t="n"/>
+      <c r="C29" s="50" t="n"/>
+      <c r="D29" s="50" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="72" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>For Balushahi: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder. Bring yogurt to a simmer gently and stir; a rolling boil can split it.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B34" s="52" t="n"/>
+      <c r="C34" s="52" t="n"/>
+      <c r="D34" s="52" t="n"/>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Cut even portions. Garnish with nuts only if the allergen card allows. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="28">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4048,7 +5480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4060,7 +5492,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Rabri</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Rabri</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4070,7 +5502,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Uttar Pradesh kitchen  ·  Dessert  ·  Awadhi, Braj and Purvanchal sattvic</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Uttar Pradesh  ·  Dessert</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4090,44 +5522,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>Hot or chilled</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>55 min</t>
+          <t>Prep 10 min · Cook 45 min</t>
         </is>
       </c>
     </row>
@@ -4275,34 +5707,187 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="66" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Reduce in heavy steel, scraping malai.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Heavy stainless steel milk pot — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="49" t="n"/>
     </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. Use a heavy stainless steel milk pot. Acidic or milk dishes must never touch aluminium.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Reduce in heavy steel, scraping malai. Work in Heavy stainless steel milk pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot or chilled.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>kcal 278  ·  Protein 9 g  ·  Carbs 39 g  ·  Fat 11 g  ·  Fibre 0 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="n"/>
+      <c r="C28" s="50" t="n"/>
+      <c r="D28" s="50" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>For Rabri: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Serve in steel or glass bowls. If chilled, take out 5 minutes before the pass. Service temperature: Hot or chilled. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="27">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4580,7 +6165,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4592,7 +6177,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Rice Kheer</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Rice Kheer</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4602,7 +6187,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Uttar Pradesh kitchen  ·  Dessert  ·  Awadhi, Braj and Purvanchal sattvic</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Uttar Pradesh  ·  Dessert</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4622,44 +6207,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>Hot or chilled</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>50 min</t>
+          <t>Prep 10 min · Cook 40 min</t>
         </is>
       </c>
     </row>
@@ -4825,35 +6410,188 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="66" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Simmer in steel.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Heavy stainless steel milk pot — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. Use a heavy stainless steel milk pot. Acidic or milk dishes must never touch aluminium.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Simmer in steel. Work in Heavy stainless steel milk pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot or chilled.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>kcal 443  ·  Protein 12 g  ·  Carbs 78 g  ·  Fat 10 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B29" s="50" t="n"/>
+      <c r="C29" s="50" t="n"/>
+      <c r="D29" s="50" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="72" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>For Rice Kheer: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B34" s="52" t="n"/>
+      <c r="C34" s="52" t="n"/>
+      <c r="D34" s="52" t="n"/>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Serve in steel or glass bowls. If chilled, take out 5 minutes before the pass. Service temperature: Hot or chilled. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="28">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4867,7 +6605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4879,7 +6617,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Thandai Cooler</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Thandai Cooler</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4889,7 +6627,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Uttar Pradesh kitchen  ·  Dessert  ·  Awadhi, Braj and Purvanchal sattvic</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Uttar Pradesh  ·  Dessert</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4909,44 +6647,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>0 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Prep 15 min · Cook 0 min</t>
         </is>
       </c>
     </row>
@@ -5148,37 +6886,216 @@
       <c r="C22" s="46" t="n"/>
       <c r="D22" s="46" t="n"/>
     </row>
-    <row r="23" ht="36" customHeight="1">
+    <row r="23" ht="54" customHeight="1">
       <c r="A23" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="48" t="inlineStr">
         <is>
-          <t>Grind masala, mix into milk. Chill. No allium.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel or glass bowl. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C23" s="49" t="n"/>
       <c r="D23" s="49" t="n"/>
     </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. Use a heavy stainless steel milk pot. Acidic or milk dishes must never touch aluminium.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Grind masala, mix into milk. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Chill. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>No allium. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="31" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="n"/>
+      <c r="C32" s="22" t="n"/>
+      <c r="D32" s="22" t="n"/>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>kcal 292  ·  Protein 10 g  ·  Carbs 40 g  ·  Fat 12 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="48" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="26" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+    </row>
+    <row r="37" ht="72" customHeight="1">
+      <c r="A37" s="25" t="inlineStr">
+        <is>
+          <t>For Thandai Cooler: keep it cold and set before service. Never store yogurt or milk sweets in aluminium. Garnish nuts only if the allergen card allows. Read spice and hing labels if used.</t>
+        </is>
+      </c>
+      <c r="B37" s="26" t="n"/>
+      <c r="C37" s="26" t="n"/>
+      <c r="D37" s="26" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B38" s="52" t="n"/>
+      <c r="C38" s="52" t="n"/>
+      <c r="D38" s="52" t="n"/>
+    </row>
+    <row r="39" ht="64" customHeight="1">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>Serve in steel or glass bowls. If chilled, take out 5 minutes before the pass. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B39" s="50" t="n"/>
+      <c r="C39" s="50" t="n"/>
+      <c r="D39" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="32">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -5192,7 +7109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5204,7 +7121,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Kachumber without Onion</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Kachumber without Onion</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5214,7 +7131,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Uttar Pradesh kitchen  ·  Salad  ·  Awadhi, Braj and Purvanchal sattvic</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Uttar Pradesh  ·  Salad</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -5234,44 +7151,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>8 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>0 min</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>8 min</t>
+          <t>Prep 8 min · Cook 0 min</t>
         </is>
       </c>
     </row>
@@ -5455,36 +7372,202 @@
       <c r="C21" s="46" t="n"/>
       <c r="D21" s="46" t="n"/>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="54" customHeight="1">
       <c r="A22" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B22" s="48" t="inlineStr">
         <is>
-          <t>Toss. No pyaaz.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel or glass bowl. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C22" s="49" t="n"/>
       <c r="D22" s="49" t="n"/>
     </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Toss. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>No pyaaz. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables stay crisp; dressing coats evenly; seasoning is bright, not flat.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Hold chilled, covered, up to 2 hours. Stir before service. Discard if it weeps heavily or smells sour beyond yogurt character. Service: Cold.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="n"/>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="22" t="n"/>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>kcal 28  ·  Protein 1 g  ·  Carbs 7 g  ·  Fat 0 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B31" s="50" t="n"/>
+      <c r="C31" s="50" t="n"/>
+      <c r="D31" s="50" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="48" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="72" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>For Kachumber without Onion: squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="26" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B36" s="52" t="n"/>
+      <c r="C36" s="52" t="n"/>
+      <c r="D36" s="52" t="n"/>
+    </row>
+    <row r="37" ht="64" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Dress at the last minute. Toss at the pass, do not send a wet bowl. Service temperature: Cold. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B37" s="50" t="n"/>
+      <c r="C37" s="50" t="n"/>
+      <c r="D37" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="30">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -5498,7 +7581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5510,7 +7593,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Boondi Raita</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Boondi Raita</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5520,7 +7603,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Uttar Pradesh kitchen  ·  Salad  ·  Awadhi, Braj and Purvanchal sattvic</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Uttar Pradesh  ·  Salad</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -5540,44 +7623,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>8 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>0 min</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>8 min</t>
+          <t>Prep 8 min · Cook 0 min</t>
         </is>
       </c>
     </row>
@@ -5743,35 +7826,201 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="54" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Mix. No onion raita.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel or glass bowl. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Mix. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>No onion raita. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables stay crisp; dressing coats evenly; seasoning is bright, not flat.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Hold chilled, covered, up to 2 hours. Stir before service. Discard if it weeps heavily or smells sour beyond yogurt character. Service: Cold.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>kcal 36  ·  Protein 2 g  ·  Carbs 3 g  ·  Fat 2 g  ·  Fibre 0 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="n"/>
+      <c r="C30" s="50" t="n"/>
+      <c r="D30" s="50" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>For Boondi Raita: squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B35" s="52" t="n"/>
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52" t="n"/>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Serve in a steel or glass bowl. Stir at the pass so it is not split or settled. Service temperature: Cold. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="29">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -5785,7 +8034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5797,7 +8046,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Sprouted Moong Salad</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Sprouted Moong Salad</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5807,7 +8056,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Uttar Pradesh kitchen  ·  Salad  ·  Awadhi, Braj and Purvanchal sattvic</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Uttar Pradesh  ·  Salad</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -5827,44 +8076,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>0 min</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>Prep 10 min · Cook 0 min</t>
         </is>
       </c>
     </row>
@@ -6030,35 +8279,201 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="54" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Toss. No onion.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel or glass bowl. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Toss. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>No onion. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables stay crisp; dressing coats evenly; seasoning is bright, not flat.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Hold chilled, covered, up to 2 hours. Stir before service. Discard if it weeps heavily or smells sour beyond yogurt character. Service: Cold.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>kcal 188  ·  Protein 13 g  ·  Carbs 34 g  ·  Fat 1 g  ·  Fibre 9 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="n"/>
+      <c r="C30" s="50" t="n"/>
+      <c r="D30" s="50" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>For Sprouted Moong Salad: squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B35" s="52" t="n"/>
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52" t="n"/>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Dress at the last minute. Toss at the pass, do not send a wet bowl. Service temperature: Cold. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="29">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -9513,7 +11928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9525,7 +11940,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Matar Kachori</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Matar Kachori</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9535,7 +11950,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Uttar Pradesh kitchen  ·  Starter  ·  Awadhi, Braj and Purvanchal sattvic</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Uttar Pradesh  ·  Starter</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -9555,44 +11970,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>50 min</t>
+          <t>Prep 30 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -9812,38 +12227,191 @@
       <c r="C23" s="46" t="n"/>
       <c r="D23" s="46" t="n"/>
     </row>
-    <row r="24" ht="36" customHeight="1">
+    <row r="24" ht="66" customHeight="1">
       <c r="A24" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B24" s="48" t="inlineStr">
         <is>
-          <t>Stuff, fry on medium in steel.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel kadhai for frying — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C24" s="49" t="n"/>
       <c r="D24" s="49" t="n"/>
     </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Stuff, fry on medium in steel. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: crust or crumb is set, centre is hot, no raw flour or potato taste. Drain on a steel rack, not paper in the fryer basket.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="n"/>
+      <c r="D29" s="31" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="22" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>kcal 326  ·  Protein 8 g  ·  Carbs 54 g  ·  Fat 8 g  ·  Fibre 4 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="72" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>For Matar Kachori: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B37" s="52" t="n"/>
+      <c r="C37" s="52" t="n"/>
+      <c r="D37" s="52" t="n"/>
+    </row>
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Serve immediately while crisp or hot. Offer a chutney or raita that is also onion-garlic free. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B38" s="50" t="n"/>
+      <c r="C38" s="50" t="n"/>
+      <c r="D38" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="C20:D20"/>
+  <mergeCells count="31">
     <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
     <mergeCell ref="A22:D22"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
-    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -9857,7 +12425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9869,7 +12437,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Palak Pakora</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Palak Pakora</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9879,7 +12447,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Uttar Pradesh kitchen  ·  Starter  ·  Awadhi, Braj and Purvanchal sattvic</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Uttar Pradesh  ·  Starter</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -9899,44 +12467,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Prep 10 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -10138,37 +12706,203 @@
       <c r="C22" s="46" t="n"/>
       <c r="D22" s="46" t="n"/>
     </row>
-    <row r="23" ht="36" customHeight="1">
+    <row r="23" ht="66" customHeight="1">
       <c r="A23" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="48" t="inlineStr">
         <is>
-          <t>Dip leaves, fry in steel.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel kadhai for frying — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C23" s="49" t="n"/>
       <c r="D23" s="49" t="n"/>
     </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. Wash greens in several changes of water; drain and squeeze dry.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Steel kadhai for frying — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Dip leaves, fry in steel. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: crust or crumb is set, centre is hot, no raw flour or potato taste. Drain on a steel rack, not paper in the fryer basket.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="22" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>kcal 224  ·  Protein 10 g  ·  Carbs 25 g  ·  Fat 10 g  ·  Fibre 5 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="72" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>Wash greens until the water is clear; grit ruins the dish. For Palak Pakora: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder. Cook or roast besan until the raw smell is gone.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B37" s="52" t="n"/>
+      <c r="C37" s="52" t="n"/>
+      <c r="D37" s="52" t="n"/>
+    </row>
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Serve immediately while crisp or hot. Offer a chutney or raita that is also onion-garlic free. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B38" s="50" t="n"/>
+      <c r="C38" s="50" t="n"/>
+      <c r="D38" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="31">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -10182,7 +12916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10194,7 +12928,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Aloo Tikki (no onion)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Aloo Tikki (no onion)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10204,7 +12938,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Uttar Pradesh kitchen  ·  Starter  ·  Awadhi, Braj and Purvanchal sattvic</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Uttar Pradesh  ·  Starter</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -10224,44 +12958,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Prep 20 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -10445,36 +13179,189 @@
       <c r="C21" s="46" t="n"/>
       <c r="D21" s="46" t="n"/>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="54" customHeight="1">
       <c r="A22" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B22" s="48" t="inlineStr">
         <is>
-          <t>Shape, pan-fry on iron.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Cast-iron tawa (not aluminium). Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C22" s="49" t="n"/>
       <c r="D22" s="49" t="n"/>
     </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. If using potato, cook until tender, drain, and steam-dry so the mix is not wet.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Shape, pan-fry on iron. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: crust or crumb is set, centre is hot, no raw flour or potato taste. Drain on a steel rack, not paper in the fryer basket.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>kcal 171  ·  Protein 4 g  ·  Carbs 23 g  ·  Fat 7 g  ·  Fibre 4 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="n"/>
+      <c r="C30" s="50" t="n"/>
+      <c r="D30" s="50" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>None identified in this spec — still verify hing brand (many contain wheat) and spice blends.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>For Aloo Tikki (no onion): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B35" s="52" t="n"/>
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52" t="n"/>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Serve immediately while crisp or hot. Offer a chutney or raita that is also onion-garlic free. Service temperature: Hot. Allergen label for this dish: None identified in this spec — still verify hing brand (many contain wheat) and spice blends. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="29">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -10488,7 +13375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10500,7 +13387,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Aloo Tamatar</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Aloo Tamatar</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10510,7 +13397,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Uttar Pradesh kitchen  ·  Main  ·  Awadhi, Braj and Purvanchal sattvic</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Uttar Pradesh  ·  Main</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -10530,44 +13417,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Prep 10 min · Cook 25 min</t>
         </is>
       </c>
     </row>
@@ -10823,40 +13710,219 @@
       <c r="C25" s="46" t="n"/>
       <c r="D25" s="46" t="n"/>
     </row>
-    <row r="26" ht="36" customHeight="1">
+    <row r="26" ht="66" customHeight="1">
       <c r="A26" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B26" s="48" t="inlineStr">
         <is>
-          <t>Tadka, tomato, potatoes, simmer. No pyaz, no lehsun.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C26" s="49" t="n"/>
       <c r="D26" s="49" t="n"/>
     </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. If using potato, cook until tender, drain, and steam-dry so the mix is not wet.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel kadhai or saucepan — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="29" ht="54" customHeight="1">
+      <c r="A29" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>Tadka, tomato, potatoes, simmer. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="n"/>
+      <c r="D29" s="31" t="n"/>
+    </row>
+    <row r="30" ht="54" customHeight="1">
+      <c r="A30" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B30" s="48" t="inlineStr">
+        <is>
+          <t>No pyaz, no lehsun. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C30" s="49" t="n"/>
+      <c r="D30" s="49" t="n"/>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B31" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C31" s="31" t="n"/>
+      <c r="D31" s="31" t="n"/>
+    </row>
+    <row r="32" ht="42" customHeight="1">
+      <c r="A32" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B32" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C32" s="49" t="n"/>
+      <c r="D32" s="49" t="n"/>
+    </row>
+    <row r="33" ht="42" customHeight="1">
+      <c r="A33" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B33" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C33" s="31" t="n"/>
+      <c r="D33" s="31" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="n"/>
+      <c r="C35" s="22" t="n"/>
+      <c r="D35" s="22" t="n"/>
+    </row>
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>kcal 161  ·  Protein 3 g  ·  Carbs 21 g  ·  Fat 7 g  ·  Fibre 3 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+    </row>
+    <row r="38" ht="48" customHeight="1">
+      <c r="A38" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="n"/>
+      <c r="C38" s="26" t="n"/>
+      <c r="D38" s="26" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n"/>
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="6" t="n"/>
+    </row>
+    <row r="40" ht="72" customHeight="1">
+      <c r="A40" s="25" t="inlineStr">
+        <is>
+          <t>For Aloo Tamatar: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B40" s="26" t="n"/>
+      <c r="C40" s="26" t="n"/>
+      <c r="D40" s="26" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B41" s="52" t="n"/>
+      <c r="C41" s="52" t="n"/>
+      <c r="D41" s="52" t="n"/>
+    </row>
+    <row r="42" ht="64" customHeight="1">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>Plate with bread or rice from the same kitchen card. Sauce should nap, not flood. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B42" s="50" t="n"/>
+      <c r="C42" s="50" t="n"/>
+      <c r="D42" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="35">
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
     <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
     <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B28:D28"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A40:D40"/>
     <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A39:D39"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="A24:D24"/>
     <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B33:D33"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="C21:D21"/>
+    <mergeCell ref="B32:D32"/>
     <mergeCell ref="B26:D26"/>
+    <mergeCell ref="A41:D41"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A42:D42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -10870,7 +13936,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10882,7 +13948,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  UP Kadhi</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · UP Kadhi</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10892,7 +13958,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Uttar Pradesh kitchen  ·  Main  ·  Awadhi, Braj and Purvanchal sattvic</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Uttar Pradesh  ·  Main</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -10912,44 +13978,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>Prep 15 min · Cook 30 min</t>
         </is>
       </c>
     </row>
@@ -11169,38 +14235,217 @@
       <c r="C23" s="46" t="n"/>
       <c r="D23" s="46" t="n"/>
     </row>
-    <row r="24" ht="36" customHeight="1">
+    <row r="24" ht="66" customHeight="1">
       <c r="A24" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B24" s="48" t="inlineStr">
         <is>
-          <t>Simmer kadhi in steel, stirring. Tadka.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C24" s="49" t="n"/>
       <c r="D24" s="49" t="n"/>
     </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel kadhai or saucepan — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Simmer kadhi in steel, stirring. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Tadka. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="n"/>
+      <c r="D29" s="31" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B30" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C30" s="49" t="n"/>
+      <c r="D30" s="49" t="n"/>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B31" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C31" s="31" t="n"/>
+      <c r="D31" s="31" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="n"/>
+      <c r="C33" s="22" t="n"/>
+      <c r="D33" s="22" t="n"/>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>kcal 180  ·  Protein 10 g  ·  Carbs 25 g  ·  Fat 4 g  ·  Fibre 4 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="48" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+    </row>
+    <row r="38" ht="72" customHeight="1">
+      <c r="A38" s="25" t="inlineStr">
+        <is>
+          <t>For UP Kadhi: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder. Bring yogurt to a simmer gently and stir; a rolling boil can split it. Cook or roast besan until the raw smell is gone.</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="n"/>
+      <c r="C38" s="26" t="n"/>
+      <c r="D38" s="26" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B39" s="52" t="n"/>
+      <c r="C39" s="52" t="n"/>
+      <c r="D39" s="52" t="n"/>
+    </row>
+    <row r="40" ht="64" customHeight="1">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>Plate with bread or rice from the same kitchen card. Sauce should nap, not flood. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B40" s="50" t="n"/>
+      <c r="C40" s="50" t="n"/>
+      <c r="D40" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="C20:D20"/>
+  <mergeCells count="33">
     <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
     <mergeCell ref="A22:D22"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
-    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A33:D33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -11214,7 +14459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11226,7 +14471,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Moong Dal Tadka</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Moong Dal Tadka</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11236,7 +14481,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Uttar Pradesh kitchen  ·  Main  ·  Awadhi, Braj and Purvanchal sattvic</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Uttar Pradesh  ·  Main</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -11256,44 +14501,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Prep 10 min · Cook 25 min</t>
         </is>
       </c>
     </row>
@@ -11513,38 +14758,217 @@
       <c r="C23" s="46" t="n"/>
       <c r="D23" s="46" t="n"/>
     </row>
-    <row r="24" ht="36" customHeight="1">
+    <row r="24" ht="66" customHeight="1">
       <c r="A24" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B24" s="48" t="inlineStr">
         <is>
-          <t>Cook dal, tadka. Temple-style.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel or clay pot — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C24" s="49" t="n"/>
       <c r="D24" s="49" t="n"/>
     </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel or clay pot — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Cook dal, tadka. Work in Stainless steel or clay pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Temple-style. Work in Stainless steel or clay pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="n"/>
+      <c r="D29" s="31" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B30" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C30" s="49" t="n"/>
+      <c r="D30" s="49" t="n"/>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B31" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C31" s="31" t="n"/>
+      <c r="D31" s="31" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="n"/>
+      <c r="C33" s="22" t="n"/>
+      <c r="D33" s="22" t="n"/>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>kcal 208  ·  Protein 10 g  ·  Carbs 27 g  ·  Fat 8 g  ·  Fibre 7 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="48" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+    </row>
+    <row r="38" ht="72" customHeight="1">
+      <c r="A38" s="25" t="inlineStr">
+        <is>
+          <t>For Moong Dal Tadka: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="n"/>
+      <c r="C38" s="26" t="n"/>
+      <c r="D38" s="26" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B39" s="52" t="n"/>
+      <c r="C39" s="52" t="n"/>
+      <c r="D39" s="52" t="n"/>
+    </row>
+    <row r="40" ht="64" customHeight="1">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>Plate with bread or rice from the same kitchen card. Sauce should nap, not flood. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B40" s="50" t="n"/>
+      <c r="C40" s="50" t="n"/>
+      <c r="D40" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="C20:D20"/>
+  <mergeCells count="33">
     <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
     <mergeCell ref="A22:D22"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
-    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A33:D33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
